--- a/artfynd/A 33574-2022 artfynd.xlsx
+++ b/artfynd/A 33574-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 33574-2022 artfynd.xlsx
+++ b/artfynd/A 33574-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,37 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>92215966</v>
+        <v>92215964</v>
       </c>
       <c r="B2" t="n">
-        <v>89356</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -726,10 +721,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>518053.2278868615</v>
+        <v>517961</v>
       </c>
       <c r="R2" t="n">
-        <v>6608732.068140888</v>
+        <v>6608604</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -759,19 +754,9 @@
           <t>2021-04-06</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2021-04-06</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -814,53 +799,59 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>112442490</v>
+        <v>92215966</v>
       </c>
       <c r="B3" t="n">
-        <v>96845</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91872</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Ålkilen, Vstm</t>
+          <t>Sågängen, Vstm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>518340</v>
+        <v>518053</v>
       </c>
       <c r="R3" t="n">
-        <v>6608985</v>
+        <v>6608732</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -884,12 +875,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2023-09-01</t>
+          <t>2021-04-06</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2023-09-30</t>
+          <t>2021-04-06</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -898,21 +889,231 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
+      <c r="AH3" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AM3" t="inlineStr">
+        <is>
+          <t>Död trädstam</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>Dead tree stem</t>
+        </is>
+      </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
+          <t>Emil Pagstedt Andersson</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Emil Pagstedt Andersson</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>112442489</v>
+      </c>
+      <c r="B4" t="n">
+        <v>80461</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>6462</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Stuplav</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Nephroma bellum</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Ålkilen, Vstm</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>518272</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6609063</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Lindesberg</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Linde</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2023-09-01</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2023-09-30</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
           <t>Alexander Singer</t>
         </is>
       </c>
-      <c r="AX3" t="inlineStr">
+      <c r="AX4" t="inlineStr">
         <is>
           <t>Alexander Singer</t>
         </is>
       </c>
-      <c r="AY3" t="inlineStr"/>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>112442490</v>
+      </c>
+      <c r="B5" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Ålkilen, Vstm</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>518340</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6608986</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Lindesberg</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Linde</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2023-09-01</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2023-09-30</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Alexander Singer</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Alexander Singer</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 33574-2022 artfynd.xlsx
+++ b/artfynd/A 33574-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AZ5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -796,6 +801,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/92215964</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -920,6 +930,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/92215966</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1017,6 +1032,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112442489</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1114,8 +1134,19 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112442490</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>